--- a/medical_surveys_questionnaires/044_covid_19_screening_survey_and_waiver--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/044_covid_19_screening_survey_and_waiver--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>medical_history_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>medical history</t>
+          <t>Medical History 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>medical_conditions</t>
+          <t>medical_conditions_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>medical conditions</t>
+          <t>Medical Conditions 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>medical_allergies</t>
+          <t>medical_allergies_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>medical allergies</t>
+          <t>Medical Allergies 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>surgical_history</t>
+          <t>surgical_history_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>surgical history</t>
+          <t>Surgical History 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>medication_history</t>
+          <t>medication_history_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>medication history</t>
+          <t>Medication History 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>have_you_ever_been_ill_with_covid</t>
+          <t>have_you_ever_been_ill_with_covid_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>have you ever been ill with covid</t>
+          <t>Have You Ever Been Ill With Covid 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>have_you_ever_been_ill_with_covid</t>
+          <t>have_you_ever_been_ill_with_covid_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>have you ever been ill with covid</t>
+          <t>Have You Ever Been Ill With Covid 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,8 +1101,8 @@
   <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1420,19 +1420,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>medical_history_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,24 +1449,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>medical_history_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,24 +1483,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>medical_conditions_choices</t>
+          <t>medical_conditions_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>medical_allergies_choices</t>
+          <t>medical_allergies_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,24 +1517,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>medical_allergies_choices</t>
+          <t>medical_allergies_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>surgical_history_choices</t>
+          <t>surgical_history_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,24 +1551,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>surgical_history_choices</t>
+          <t>surgical_history_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>medication_history_choices</t>
+          <t>medication_history_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,17 +1585,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>medication_history_choices</t>
+          <t>medication_history_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1760,19 +1760,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>have_you_ever_been_ill_with_covid_choices</t>
+          <t>have_you_ever_been_ill_with_covid_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,24 +1789,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>have_you_ever_been_ill_with_covid_choices</t>
+          <t>have_you_ever_been_ill_with_covid_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>have_you_ever_been_ill_with_covid_choices</t>
+          <t>have_you_ever_been_ill_with_covid_3_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,17 +1823,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>have_you_ever_been_ill_with_covid_choices</t>
+          <t>have_you_ever_been_ill_with_covid_3_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
